--- a/data/trans_orig/P5705-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5705-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir amor y afecto en 2007</t>
+          <t>Población según la frecuencia de recibir amor y afecto en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>367578</t>
+          <t>364048</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>416953</t>
+          <t>415920</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>318873</t>
+          <t>314053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>371707</t>
+          <t>370785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>699246</t>
+          <t>702421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>774733</t>
+          <t>774089</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>192768</t>
+          <t>191947</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238626</t>
+          <t>239720</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>204538</t>
+          <t>205149</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255183</t>
+          <t>256236</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>411597</t>
+          <t>410632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>482851</t>
+          <t>479258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,69%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56445</t>
+          <t>57071</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87716</t>
+          <t>87496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61498</t>
+          <t>62711</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>92607</t>
+          <t>95151</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>127239</t>
+          <t>125695</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>171092</t>
+          <t>171889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>10265</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>27531</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>18405</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38348</t>
+          <t>39360</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31822</t>
+          <t>32579</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58239</t>
+          <t>61455</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>12794</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13997</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>559164</t>
+          <t>563606</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>620629</t>
+          <t>625019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>548528</t>
+          <t>551554</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>612688</t>
+          <t>615186</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1126150</t>
+          <t>1132600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1213725</t>
+          <t>1218217</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>63,11%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>212734</t>
+          <t>213568</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>267095</t>
+          <t>267305</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>241746</t>
+          <t>239269</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>299423</t>
+          <t>296579</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>470746</t>
+          <t>469188</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>549162</t>
+          <t>550296</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84797</t>
+          <t>82674</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>123753</t>
+          <t>123492</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77029</t>
+          <t>77284</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115716</t>
+          <t>117295</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>173607</t>
+          <t>172672</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>227166</t>
+          <t>225886</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14003</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33305</t>
+          <t>34808</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31777</t>
+          <t>33307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32494</t>
+          <t>31124</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59522</t>
+          <t>60254</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11054</t>
+          <t>12186</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12243</t>
+          <t>13367</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>433325</t>
+          <t>434198</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>483499</t>
+          <t>486381</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>414312</t>
+          <t>415141</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>461837</t>
+          <t>463590</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>861994</t>
+          <t>862066</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>933673</t>
+          <t>933256</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,5%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128501</t>
+          <t>127665</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>172261</t>
+          <t>171478</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135397</t>
+          <t>135699</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>177856</t>
+          <t>177726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>277142</t>
+          <t>274411</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>341005</t>
+          <t>336885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36670</t>
+          <t>36237</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66282</t>
+          <t>65713</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53558</t>
+          <t>53089</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82986</t>
+          <t>83948</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>95359</t>
+          <t>97358</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>137423</t>
+          <t>140873</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26618</t>
+          <t>26452</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32467</t>
+          <t>32813</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27017</t>
+          <t>25950</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52406</t>
+          <t>53618</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,62 +2584,62 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2631</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1884</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2631</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>8829</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>530379</t>
+          <t>532792</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>590730</t>
+          <t>593755</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>594336</t>
+          <t>592719</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>659039</t>
+          <t>656227</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1143255</t>
+          <t>1146105</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1229573</t>
+          <t>1226069</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,93%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>234770</t>
+          <t>233014</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>287110</t>
+          <t>288114</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>226941</t>
+          <t>228070</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>285014</t>
+          <t>283606</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>476655</t>
+          <t>475990</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>555684</t>
+          <t>554536</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66399</t>
+          <t>66563</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>101455</t>
+          <t>100546</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>95231</t>
+          <t>92772</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>134067</t>
+          <t>133630</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>168754</t>
+          <t>169869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>222537</t>
+          <t>222315</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25574</t>
+          <t>24927</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48179</t>
+          <t>47038</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27092</t>
+          <t>27533</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52051</t>
+          <t>53962</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>58260</t>
+          <t>59079</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91137</t>
+          <t>91242</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>854</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12408</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18708</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1949335</t>
+          <t>1949999</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2059542</t>
+          <t>2062645</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1940706</t>
+          <t>1938915</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2052893</t>
+          <t>2052968</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3915963</t>
+          <t>3924467</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4081276</t>
+          <t>4080680</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,33%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>817107</t>
+          <t>813580</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>919053</t>
+          <t>919511</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>856758</t>
+          <t>855486</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>956912</t>
+          <t>958506</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1702049</t>
+          <t>1707370</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1835490</t>
+          <t>1843269</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>276139</t>
+          <t>272018</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>341793</t>
+          <t>339313</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>317852</t>
+          <t>317611</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>392246</t>
+          <t>387759</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>606846</t>
+          <t>606196</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>707426</t>
+          <t>706554</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>72955</t>
+          <t>73232</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>112542</t>
+          <t>112826</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>90036</t>
+          <t>90456</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>132610</t>
+          <t>131084</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>173724</t>
+          <t>169916</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>232393</t>
+          <t>229169</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20738</t>
+          <t>20247</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20812</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>15138</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>35678</t>
+          <t>35077</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir amor y afecto en 2012</t>
+          <t>Población según la frecuencia de recibir amor y afecto en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>499799</t>
+          <t>499163</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>546402</t>
+          <t>547645</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>447481</t>
+          <t>446097</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>499354</t>
+          <t>496488</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>963246</t>
+          <t>963360</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1031537</t>
+          <t>1032838</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,91%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110254</t>
+          <t>110155</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>152998</t>
+          <t>153002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137980</t>
+          <t>143014</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>185266</t>
+          <t>189114</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>260528</t>
+          <t>262748</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>322674</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22159</t>
+          <t>23049</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45563</t>
+          <t>45571</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30844</t>
+          <t>29518</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57315</t>
+          <t>56120</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59662</t>
+          <t>58352</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>93354</t>
+          <t>93590</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16020</t>
+          <t>16210</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22992</t>
+          <t>24262</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,47 +4764,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>23190</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>14814</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>34726</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>1,06%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>23190</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>14836</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>32692</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>10287</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13459</t>
+          <t>12989</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>626816</t>
+          <t>624395</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>689516</t>
+          <t>692711</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>647800</t>
+          <t>648415</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>712464</t>
+          <t>711323</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1293898</t>
+          <t>1295554</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1387697</t>
+          <t>1386416</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237511</t>
+          <t>236338</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>293348</t>
+          <t>294190</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244078</t>
+          <t>242939</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>304199</t>
+          <t>300412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>495396</t>
+          <t>493888</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>578237</t>
+          <t>578595</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60769</t>
+          <t>62544</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95903</t>
+          <t>99289</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49968</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82047</t>
+          <t>83828</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>121831</t>
+          <t>121162</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>165987</t>
+          <t>166480</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22802</t>
+          <t>22858</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18164</t>
+          <t>17513</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13209</t>
+          <t>13625</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34089</t>
+          <t>34767</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -5509,82 +5509,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2138</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2087</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6466</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>2138</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7519</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2138</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7569</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>476383</t>
+          <t>477392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>533822</t>
+          <t>531977</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>471343</t>
+          <t>473726</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>530710</t>
+          <t>531563</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>971934</t>
+          <t>972034</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1052947</t>
+          <t>1048187</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,53%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147354</t>
+          <t>147038</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195936</t>
+          <t>195410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177637</t>
+          <t>176675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>228727</t>
+          <t>229354</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>336679</t>
+          <t>335405</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>409046</t>
+          <t>409190</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44702</t>
+          <t>45165</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78651</t>
+          <t>79880</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41383</t>
+          <t>42215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71027</t>
+          <t>71973</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93283</t>
+          <t>92688</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>139000</t>
+          <t>137219</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19368</t>
+          <t>18529</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22455</t>
+          <t>22561</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14978</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34671</t>
+          <t>34890</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>13056</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16888</t>
+          <t>18248</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>529650</t>
+          <t>530409</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>591959</t>
+          <t>593037</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>562393</t>
+          <t>562643</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>627193</t>
+          <t>627116</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1114355</t>
+          <t>1112715</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1201028</t>
+          <t>1200896</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245738</t>
+          <t>242232</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>303066</t>
+          <t>300501</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>296978</t>
+          <t>298235</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>358940</t>
+          <t>359460</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>558823</t>
+          <t>558444</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>642669</t>
+          <t>640412</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74681</t>
+          <t>74853</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>115524</t>
+          <t>113554</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>81990</t>
+          <t>81040</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>118672</t>
+          <t>119997</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>165236</t>
+          <t>165626</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>218774</t>
+          <t>218969</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21888</t>
+          <t>22943</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27900</t>
+          <t>28530</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>18606</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44543</t>
+          <t>43081</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14997</t>
+          <t>15484</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17503</t>
+          <t>17812</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26353</t>
+          <t>27331</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2195400</t>
+          <t>2194124</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2312513</t>
+          <t>2310775</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2197594</t>
+          <t>2198803</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2311001</t>
+          <t>2314512</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4430795</t>
+          <t>4421391</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4592521</t>
+          <t>4593506</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,96%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>786114</t>
+          <t>785495</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>895139</t>
+          <t>892456</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>905133</t>
+          <t>908038</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1015362</t>
+          <t>1016390</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1727975</t>
+          <t>1721892</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1874642</t>
+          <t>1869243</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>233662</t>
+          <t>230161</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>298519</t>
+          <t>300118</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>233300</t>
+          <t>231230</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>297858</t>
+          <t>295127</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>479842</t>
+          <t>475080</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>569049</t>
+          <t>572990</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>33131</t>
+          <t>33412</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>61490</t>
+          <t>61358</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>40266</t>
+          <t>40578</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>70276</t>
+          <t>71524</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>79001</t>
+          <t>80567</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>118999</t>
+          <t>121829</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>28258</t>
+          <t>27186</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10141</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28142</t>
+          <t>28446</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>22987</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>47295</t>
+          <t>47350</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir amor y afecto en 2016</t>
+          <t>Población según la frecuencia de recibir amor y afecto en 2016 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>295096</t>
+          <t>297432</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>347715</t>
+          <t>347270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>279573</t>
+          <t>279145</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>330897</t>
+          <t>332919</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>591795</t>
+          <t>591772</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>659976</t>
+          <t>663978</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,42%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223058</t>
+          <t>221427</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>276567</t>
+          <t>271281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>226659</t>
+          <t>227424</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277694</t>
+          <t>279702</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>465414</t>
+          <t>468226</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>533610</t>
+          <t>536328</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63794</t>
+          <t>62333</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>98338</t>
+          <t>98709</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81469</t>
+          <t>79575</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>118362</t>
+          <t>116471</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152693</t>
+          <t>153019</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>200150</t>
+          <t>202229</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>10238</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29369</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16675</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17316</t>
+          <t>17954</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39223</t>
+          <t>39675</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>12763</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19826</t>
+          <t>20758</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>564608</t>
+          <t>564808</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>628938</t>
+          <t>629813</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>549843</t>
+          <t>549629</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>616048</t>
+          <t>614449</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1134668</t>
+          <t>1135549</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1230639</t>
+          <t>1226492</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>267761</t>
+          <t>268223</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>328573</t>
+          <t>327435</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>296406</t>
+          <t>297470</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>359090</t>
+          <t>359380</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>575962</t>
+          <t>584717</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>666653</t>
+          <t>669665</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77723</t>
+          <t>77432</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>115043</t>
+          <t>114439</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>92345</t>
+          <t>91480</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134443</t>
+          <t>133298</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>180547</t>
+          <t>179146</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>234404</t>
+          <t>234965</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16713</t>
+          <t>16803</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36030</t>
+          <t>36745</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12191</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30799</t>
+          <t>30063</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32991</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60074</t>
+          <t>61752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14329</t>
+          <t>14844</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15866</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>350316</t>
+          <t>352071</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>406115</t>
+          <t>406724</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>333776</t>
+          <t>338205</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>391262</t>
+          <t>393001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>702632</t>
+          <t>704946</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>783616</t>
+          <t>783123</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>221102</t>
+          <t>221442</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>273103</t>
+          <t>271747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>241713</t>
+          <t>241209</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>298774</t>
+          <t>298057</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>478465</t>
+          <t>478774</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>556483</t>
+          <t>555667</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>99192</t>
+          <t>99602</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>141090</t>
+          <t>143349</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>112936</t>
+          <t>113153</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>155302</t>
+          <t>156489</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>224309</t>
+          <t>224262</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>283500</t>
+          <t>284171</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>21712</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,82 +9735,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>8770</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>3401</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>15755</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>20774</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>13034</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>31479</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>8770</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>4063</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>17201</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>20774</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>13484</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>32304</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10371</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>868</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>10746</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>520209</t>
+          <t>519850</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>580566</t>
+          <t>577997</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>571395</t>
+          <t>570721</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>638574</t>
+          <t>637100</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1109796</t>
+          <t>1109541</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1203517</t>
+          <t>1198468</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,56%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>235636</t>
+          <t>235335</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>288440</t>
+          <t>288465</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>267807</t>
+          <t>267141</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>326755</t>
+          <t>327310</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>515788</t>
+          <t>517878</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>596819</t>
+          <t>597991</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>81281</t>
+          <t>82504</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>117988</t>
+          <t>119540</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>86633</t>
+          <t>87869</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>128431</t>
+          <t>131994</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>178086</t>
+          <t>180715</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>235733</t>
+          <t>232722</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25843</t>
+          <t>26852</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19852</t>
+          <t>19145</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42565</t>
+          <t>42997</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34169</t>
+          <t>33123</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62937</t>
+          <t>60636</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>14333</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16183</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>24482</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1791049</t>
+          <t>1793145</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1908907</t>
+          <t>1909871</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1794653</t>
+          <t>1795302</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1923884</t>
+          <t>1914346</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3625939</t>
+          <t>3613463</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3799546</t>
+          <t>3785186</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,68%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>998564</t>
+          <t>996013</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1105035</t>
+          <t>1105638</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1082788</t>
+          <t>1086227</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1202854</t>
+          <t>1202658</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2111752</t>
+          <t>2120138</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2272279</t>
+          <t>2282974</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>359223</t>
+          <t>359576</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>436736</t>
+          <t>432975</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>408320</t>
+          <t>409853</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>491519</t>
+          <t>489918</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>785159</t>
+          <t>792004</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>895446</t>
+          <t>905150</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>56737</t>
+          <t>55860</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>91628</t>
+          <t>91829</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,82 +11099,82 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>66987</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>52234</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>85962</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>138772</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>115928</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>163480</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>66987</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>52297</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>84962</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>138772</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>117772</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>166374</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12473</t>
+          <t>12886</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30547</t>
+          <t>31352</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27419</t>
+          <t>28281</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>25450</t>
+          <t>26034</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>51830</t>
+          <t>50579</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir amor y afecto en 2023</t>
+          <t>Población según la frecuencia de recibir amor y afecto en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>374223</t>
+          <t>373865</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>423155</t>
+          <t>423865</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>383962</t>
+          <t>381530</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>423424</t>
+          <t>424414</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>769448</t>
+          <t>770286</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>832524</t>
+          <t>833321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,78%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140669</t>
+          <t>137912</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>182280</t>
+          <t>182558</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172045</t>
+          <t>172153</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>207360</t>
+          <t>208866</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>321975</t>
+          <t>319892</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>378461</t>
+          <t>377382</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33370</t>
+          <t>33267</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57243</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44009</t>
+          <t>44350</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>66103</t>
+          <t>65541</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83220</t>
+          <t>83372</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113069</t>
+          <t>115507</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12690</t>
+          <t>12549</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29922</t>
+          <t>29781</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27346</t>
+          <t>27114</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32077</t>
+          <t>31289</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52701</t>
+          <t>52713</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17991</t>
+          <t>17781</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11894</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24818</t>
+          <t>25189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>733252</t>
+          <t>729707</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>996317</t>
+          <t>1011833</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>534100</t>
+          <t>531535</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>584937</t>
+          <t>585768</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1285012</t>
+          <t>1284813</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1644499</t>
+          <t>1644208</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,48%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151508</t>
+          <t>140678</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>361043</t>
+          <t>363338</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>273627</t>
+          <t>270984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321201</t>
+          <t>321338</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>380943</t>
+          <t>386414</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658463</t>
+          <t>659260</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24140</t>
+          <t>22013</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63699</t>
+          <t>64017</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53591</t>
+          <t>52886</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79743</t>
+          <t>79979</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>76678</t>
+          <t>76099</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>134933</t>
+          <t>133665</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>11950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35916</t>
+          <t>36926</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22469</t>
+          <t>21917</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39579</t>
+          <t>39762</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35911</t>
+          <t>36317</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68849</t>
+          <t>69535</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>25093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>438997</t>
+          <t>435045</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>494506</t>
+          <t>491162</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>271845</t>
+          <t>256051</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>641726</t>
+          <t>645633</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>622450</t>
+          <t>571986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1110078</t>
+          <t>1110116</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159911</t>
+          <t>159804</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>213615</t>
+          <t>212205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>210854</t>
+          <t>207549</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>630750</t>
+          <t>650650</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>392434</t>
+          <t>394452</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>937287</t>
+          <t>995626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18244</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38830</t>
+          <t>39697</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20804</t>
+          <t>19877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63350</t>
+          <t>63241</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48171</t>
+          <t>44962</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>94227</t>
+          <t>91907</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32042</t>
+          <t>32559</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25802</t>
+          <t>25962</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26173</t>
+          <t>23756</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52369</t>
+          <t>51986</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1674</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>9399</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12488</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>555165</t>
+          <t>553340</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>614711</t>
+          <t>611266</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>675433</t>
+          <t>671630</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>782542</t>
+          <t>783337</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1245062</t>
+          <t>1245327</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1381931</t>
+          <t>1374055</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,07%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>204899</t>
+          <t>207901</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>260389</t>
+          <t>260024</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>208323</t>
+          <t>206299</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>288014</t>
+          <t>288934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>427724</t>
+          <t>436058</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>531177</t>
+          <t>532656</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47024</t>
+          <t>46010</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>75267</t>
+          <t>74696</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,82 +13946,82 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>8,06%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>62954</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>47858</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>77964</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>121947</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>102306</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>141198</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>5,07%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>62954</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>48298</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>77801</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>121947</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>102387</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>143056</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27108</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49690</t>
+          <t>48020</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32045</t>
+          <t>32589</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56645</t>
+          <t>58227</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65623</t>
+          <t>64728</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>97716</t>
+          <t>98325</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9833</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25856</t>
+          <t>25941</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9053</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20756</t>
+          <t>20388</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22260</t>
+          <t>21843</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40662</t>
+          <t>40734</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2170832</t>
+          <t>2169161</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2544350</t>
+          <t>2556797</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1787253</t>
+          <t>1754344</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2315907</t>
+          <t>2322690</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4063564</t>
+          <t>4060136</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4695560</t>
+          <t>4717038</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,33%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>666996</t>
+          <t>658539</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>939613</t>
+          <t>941043</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>954194</t>
+          <t>950691</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1566903</t>
+          <t>1642442</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1774279</t>
+          <t>1751425</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2455883</t>
+          <t>2456323</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>139290</t>
+          <t>141997</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>210197</t>
+          <t>209352</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>184914</t>
+          <t>181287</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>257889</t>
+          <t>253925</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>349063</t>
+          <t>343444</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>445911</t>
+          <t>444644</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>79463</t>
+          <t>76777</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>126134</t>
+          <t>123938</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>88852</t>
+          <t>88489</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>129809</t>
+          <t>131191</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>184953</t>
+          <t>184483</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>246076</t>
+          <t>248875</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>26930</t>
+          <t>26896</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>52682</t>
+          <t>51303</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14859,7 +14859,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>23719</t>
+          <t>23161</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41685</t>
+          <t>41154</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>55252</t>
+          <t>54987</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>85385</t>
+          <t>85450</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">

--- a/data/trans_orig/P5705-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5705-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>364048</t>
+          <t>364486</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>415920</t>
+          <t>415125</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>314053</t>
+          <t>320875</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>370785</t>
+          <t>373180</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>702421</t>
+          <t>701391</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>774089</t>
+          <t>775196</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>191947</t>
+          <t>193223</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>239720</t>
+          <t>240620</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>205149</t>
+          <t>206852</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256236</t>
+          <t>255158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>410632</t>
+          <t>411337</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>479258</t>
+          <t>480600</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57071</t>
+          <t>56745</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87496</t>
+          <t>89368</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62711</t>
+          <t>61631</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>95151</t>
+          <t>93940</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>125695</t>
+          <t>124921</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>171889</t>
+          <t>172052</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10265</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27531</t>
+          <t>27592</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,47 +1087,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>27266</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>18160</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>40835</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>3,97%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>27266</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18405</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>39360</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32579</t>
+          <t>31224</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61455</t>
+          <t>58062</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13926</t>
+          <t>14452</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>563606</t>
+          <t>560610</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>625019</t>
+          <t>623523</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>551554</t>
+          <t>548917</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>615186</t>
+          <t>612533</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1132600</t>
+          <t>1130000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1218217</t>
+          <t>1221885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,3%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>213568</t>
+          <t>213143</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>267305</t>
+          <t>268944</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>239269</t>
+          <t>242468</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>296579</t>
+          <t>298810</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>469188</t>
+          <t>471828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>550296</t>
+          <t>553377</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82674</t>
+          <t>84414</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>123492</t>
+          <t>124116</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77284</t>
+          <t>77007</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>117295</t>
+          <t>116734</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>172672</t>
+          <t>172274</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>225886</t>
+          <t>224289</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13606</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34808</t>
+          <t>32855</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13780</t>
+          <t>13598</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33307</t>
+          <t>33726</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31124</t>
+          <t>31032</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60254</t>
+          <t>58061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13367</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>434198</t>
+          <t>434706</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>486381</t>
+          <t>485094</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>415141</t>
+          <t>415130</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>463590</t>
+          <t>462828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>862066</t>
+          <t>861036</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>933256</t>
+          <t>934537</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,6%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127665</t>
+          <t>128802</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171478</t>
+          <t>173376</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135699</t>
+          <t>136580</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>177726</t>
+          <t>177908</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274411</t>
+          <t>275259</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>336885</t>
+          <t>337033</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36237</t>
+          <t>37270</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65713</t>
+          <t>65583</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53089</t>
+          <t>52233</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83948</t>
+          <t>83505</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>97358</t>
+          <t>97119</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>140873</t>
+          <t>137413</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26452</t>
+          <t>27356</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>13753</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32813</t>
+          <t>32291</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25950</t>
+          <t>27515</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53618</t>
+          <t>54506</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>532792</t>
+          <t>528001</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>593755</t>
+          <t>589544</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>592719</t>
+          <t>592824</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>656227</t>
+          <t>658221</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1146105</t>
+          <t>1138215</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1226069</t>
+          <t>1226268</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,94%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233014</t>
+          <t>232385</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>288114</t>
+          <t>288074</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>228070</t>
+          <t>227741</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>283606</t>
+          <t>283191</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>475990</t>
+          <t>477611</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>554536</t>
+          <t>553726</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66563</t>
+          <t>66735</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100546</t>
+          <t>100395</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>92772</t>
+          <t>94725</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>133630</t>
+          <t>136500</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>169869</t>
+          <t>167105</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>222315</t>
+          <t>222592</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24927</t>
+          <t>25878</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47038</t>
+          <t>48129</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27533</t>
+          <t>27663</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53962</t>
+          <t>53987</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59079</t>
+          <t>56971</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91242</t>
+          <t>90423</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>851</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1949999</t>
+          <t>1945701</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2062645</t>
+          <t>2064243</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1938915</t>
+          <t>1935619</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2052968</t>
+          <t>2049435</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3924467</t>
+          <t>3916701</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4080680</t>
+          <t>4081965</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>813580</t>
+          <t>814065</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>919511</t>
+          <t>918249</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>855486</t>
+          <t>857140</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>958506</t>
+          <t>960851</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1707370</t>
+          <t>1705421</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1843269</t>
+          <t>1847264</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>272018</t>
+          <t>272134</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>339313</t>
+          <t>341723</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>317611</t>
+          <t>317970</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>387759</t>
+          <t>390440</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>606196</t>
+          <t>611509</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>706554</t>
+          <t>711981</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>73232</t>
+          <t>72529</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>112826</t>
+          <t>110149</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>90456</t>
+          <t>89766</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>131084</t>
+          <t>131246</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>169916</t>
+          <t>174891</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>229169</t>
+          <t>232929</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>21470</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,49 +3928,49 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>12346</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>20921</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>12346</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>21022</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>22</t>
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>35077</t>
+          <t>36255</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>499163</t>
+          <t>501102</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>547645</t>
+          <t>547450</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>446097</t>
+          <t>446206</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>496488</t>
+          <t>496475</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>963360</t>
+          <t>964259</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1032838</t>
+          <t>1033785</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,97%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110155</t>
+          <t>111527</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>153002</t>
+          <t>152599</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>143014</t>
+          <t>143657</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>189114</t>
+          <t>188945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>262748</t>
+          <t>261808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>322674</t>
+          <t>325743</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23049</t>
+          <t>23131</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45571</t>
+          <t>45031</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29518</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>57398</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>58352</t>
+          <t>58721</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>93590</t>
+          <t>94348</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16210</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24262</t>
+          <t>23605</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14814</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34726</t>
+          <t>33737</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10287</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12989</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>624395</t>
+          <t>626745</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>692711</t>
+          <t>690036</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>648415</t>
+          <t>647308</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>711323</t>
+          <t>710021</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1295554</t>
+          <t>1296445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1386416</t>
+          <t>1383450</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>236338</t>
+          <t>236497</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>294190</t>
+          <t>294125</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>242939</t>
+          <t>241926</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>300412</t>
+          <t>301894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>493888</t>
+          <t>496541</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>578595</t>
+          <t>578013</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62544</t>
+          <t>61182</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99289</t>
+          <t>96133</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>51105</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83828</t>
+          <t>83406</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>121162</t>
+          <t>120916</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>166480</t>
+          <t>169784</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22858</t>
+          <t>24314</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17513</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13625</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34767</t>
+          <t>34501</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>477392</t>
+          <t>476177</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>531977</t>
+          <t>531928</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>473726</t>
+          <t>474792</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>531563</t>
+          <t>531504</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>972034</t>
+          <t>972729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1048187</t>
+          <t>1048937</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,58%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147038</t>
+          <t>149067</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195410</t>
+          <t>196575</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176675</t>
+          <t>175381</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>229354</t>
+          <t>228607</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>335405</t>
+          <t>340049</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>409190</t>
+          <t>407514</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45165</t>
+          <t>45223</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79880</t>
+          <t>76632</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42215</t>
+          <t>42413</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71973</t>
+          <t>71461</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>92688</t>
+          <t>95101</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>137219</t>
+          <t>137529</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18529</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22561</t>
+          <t>22444</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>14325</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34890</t>
+          <t>34349</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>13725</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9184</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18248</t>
+          <t>17791</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>530409</t>
+          <t>533596</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>594900</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>562643</t>
+          <t>557607</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>627116</t>
+          <t>624118</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1112715</t>
+          <t>1120392</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1200896</t>
+          <t>1205597</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,48%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>242232</t>
+          <t>240766</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>300501</t>
+          <t>299527</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>298235</t>
+          <t>295920</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>359460</t>
+          <t>357535</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>558444</t>
+          <t>553934</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>640412</t>
+          <t>637380</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74853</t>
+          <t>76176</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113554</t>
+          <t>112299</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>81040</t>
+          <t>79598</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>119997</t>
+          <t>120768</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>165626</t>
+          <t>167707</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>218969</t>
+          <t>219105</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22943</t>
+          <t>21527</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28530</t>
+          <t>29611</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18606</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43081</t>
+          <t>44692</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>14510</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17812</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>9647</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27331</t>
+          <t>26678</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2194124</t>
+          <t>2196309</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2310775</t>
+          <t>2310050</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2198803</t>
+          <t>2194251</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2314512</t>
+          <t>2308964</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4421391</t>
+          <t>4421098</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4593506</t>
+          <t>4589553</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,9%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>785495</t>
+          <t>788482</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>892456</t>
+          <t>893409</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>908038</t>
+          <t>912833</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1016390</t>
+          <t>1020906</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1721892</t>
+          <t>1718464</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1869243</t>
+          <t>1873920</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>230161</t>
+          <t>231941</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>300118</t>
+          <t>296441</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>231230</t>
+          <t>231900</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>295127</t>
+          <t>296303</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>475080</t>
+          <t>481442</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>572990</t>
+          <t>572978</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>33412</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>61358</t>
+          <t>61652</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>40578</t>
+          <t>39507</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>71524</t>
+          <t>70430</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,47 +7492,47 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>98648</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>79321</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>122275</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>98648</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>80567</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>121829</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27186</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28446</t>
+          <t>28066</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>23003</t>
+          <t>24079</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>47350</t>
+          <t>48467</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>297432</t>
+          <t>297471</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>347270</t>
+          <t>348701</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>279145</t>
+          <t>276902</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>332919</t>
+          <t>328600</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>591772</t>
+          <t>592230</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>663978</t>
+          <t>666636</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,61%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>221427</t>
+          <t>225227</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>271281</t>
+          <t>274876</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>227424</t>
+          <t>228844</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279702</t>
+          <t>278486</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>468226</t>
+          <t>461972</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>536328</t>
+          <t>534056</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,75%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62333</t>
+          <t>65019</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>98709</t>
+          <t>98493</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79575</t>
+          <t>81571</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>116471</t>
+          <t>116868</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>153019</t>
+          <t>152926</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>202229</t>
+          <t>202370</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10238</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>28833</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>15852</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17954</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39675</t>
+          <t>40221</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11480</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12763</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20758</t>
+          <t>19809</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>564808</t>
+          <t>564981</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>629813</t>
+          <t>631695</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>549629</t>
+          <t>550760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>614449</t>
+          <t>614772</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1135549</t>
+          <t>1132961</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1226492</t>
+          <t>1223849</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>268223</t>
+          <t>270932</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>327435</t>
+          <t>328124</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>297470</t>
+          <t>293828</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>359380</t>
+          <t>355773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>584717</t>
+          <t>580719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>669665</t>
+          <t>668965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77432</t>
+          <t>76419</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>114439</t>
+          <t>115586</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>91480</t>
+          <t>92216</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133298</t>
+          <t>131404</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>179146</t>
+          <t>177960</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>234965</t>
+          <t>236011</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16803</t>
+          <t>16932</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36745</t>
+          <t>35965</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>30051</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33238</t>
+          <t>32604</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61752</t>
+          <t>58649</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14844</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15697</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>352071</t>
+          <t>350151</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>406724</t>
+          <t>407045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>338205</t>
+          <t>335124</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>393001</t>
+          <t>393153</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>704946</t>
+          <t>703069</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>783123</t>
+          <t>784501</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,05%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>221442</t>
+          <t>219097</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>271747</t>
+          <t>271403</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>241209</t>
+          <t>244609</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>298057</t>
+          <t>296130</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>478774</t>
+          <t>478415</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>555667</t>
+          <t>553758</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>99602</t>
+          <t>101757</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>143349</t>
+          <t>142600</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>113153</t>
+          <t>114149</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>156489</t>
+          <t>156544</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>224262</t>
+          <t>223016</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>284171</t>
+          <t>282851</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21712</t>
+          <t>21098</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>18447</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13034</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31479</t>
+          <t>31390</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>865</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10746</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>519850</t>
+          <t>520252</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>577997</t>
+          <t>581246</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>570721</t>
+          <t>571698</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>637100</t>
+          <t>635402</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1109541</t>
+          <t>1111818</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1198468</t>
+          <t>1196381</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,45%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>235335</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>288465</t>
+          <t>290676</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>267141</t>
+          <t>268005</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>327310</t>
+          <t>328792</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>517878</t>
+          <t>517969</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>597991</t>
+          <t>598530</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82504</t>
+          <t>82071</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>119540</t>
+          <t>118264</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>87869</t>
+          <t>88280</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>131994</t>
+          <t>130950</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>180715</t>
+          <t>178238</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>232722</t>
+          <t>233734</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9837</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26852</t>
+          <t>25893</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,47 +10417,47 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>29950</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>19752</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>43314</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>2,87%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>29950</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>19145</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33123</t>
+          <t>33281</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60636</t>
+          <t>62065</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14333</t>
+          <t>14051</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15896</t>
+          <t>16946</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24482</t>
+          <t>25002</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1793145</t>
+          <t>1791715</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1909871</t>
+          <t>1906950</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1795302</t>
+          <t>1797556</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1914346</t>
+          <t>1921192</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3613463</t>
+          <t>3625281</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3785186</t>
+          <t>3792497</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,79%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>996013</t>
+          <t>998239</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1105638</t>
+          <t>1108823</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1086227</t>
+          <t>1085908</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1202658</t>
+          <t>1201620</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2120138</t>
+          <t>2119172</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2282974</t>
+          <t>2272215</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>359576</t>
+          <t>359951</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>432975</t>
+          <t>434630</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>409853</t>
+          <t>409674</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>489918</t>
+          <t>489480</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>792004</t>
+          <t>790211</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>905150</t>
+          <t>903702</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>55860</t>
+          <t>55626</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>91829</t>
+          <t>90216</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>52234</t>
+          <t>52415</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>85962</t>
+          <t>85616</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>115928</t>
+          <t>116072</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>163480</t>
+          <t>166726</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12886</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>31352</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,82 +11212,82 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>17223</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>9417</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>27840</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>37212</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>26327</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>52205</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>17223</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>10041</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>28281</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>37212</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>26034</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>50579</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -11654,32 +11654,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>398131</t>
+          <t>425106</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>373865</t>
+          <t>398433</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>423865</t>
+          <t>452613</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,32 +11689,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>403621</t>
+          <t>435054</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>381530</t>
+          <t>412744</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>424414</t>
+          <t>454854</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>801753</t>
+          <t>860160</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>770286</t>
+          <t>823453</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>833321</t>
+          <t>892918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>62,93%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>160003</t>
+          <t>177559</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>137912</t>
+          <t>155821</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>182558</t>
+          <t>201400</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>189061</t>
+          <t>206675</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172153</t>
+          <t>187424</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>208866</t>
+          <t>225846</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>349064</t>
+          <t>384234</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>319892</t>
+          <t>355083</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>377382</t>
+          <t>417290</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44075</t>
+          <t>49870</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33267</t>
+          <t>37393</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>65452</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54182</t>
+          <t>58331</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44350</t>
+          <t>47922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65541</t>
+          <t>70180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>98257</t>
+          <t>108201</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83372</t>
+          <t>91470</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115507</t>
+          <t>128143</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>14244</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29781</t>
+          <t>34648</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>22791</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>16200</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27114</t>
+          <t>30562</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>40132</t>
+          <t>46015</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31289</t>
+          <t>35427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>60373</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17781</t>
+          <t>20419</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>17390</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>13291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25189</t>
+          <t>28238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>633298</t>
+          <t>688562</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>633298</t>
+          <t>688562</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>633298</t>
+          <t>688562</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>673297</t>
+          <t>730441</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>673297</t>
+          <t>730441</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>673297</t>
+          <t>730441</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1306596</t>
+          <t>1419002</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1306596</t>
+          <t>1419002</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1306596</t>
+          <t>1419002</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>835832</t>
+          <t>637510</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>729707</t>
+          <t>603587</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1011833</t>
+          <t>673645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>559239</t>
+          <t>608920</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>531535</t>
+          <t>578588</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>585768</t>
+          <t>635991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1395071</t>
+          <t>1246430</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1284813</t>
+          <t>1203910</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1644208</t>
+          <t>1289219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>60,85%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>277706</t>
+          <t>312256</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140678</t>
+          <t>280511</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>363338</t>
+          <t>343452</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>295882</t>
+          <t>341907</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>270984</t>
+          <t>317430</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321338</t>
+          <t>369545</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>573588</t>
+          <t>654163</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>386414</t>
+          <t>617200</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>659260</t>
+          <t>693457</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46103</t>
+          <t>55290</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22013</t>
+          <t>41988</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64017</t>
+          <t>70413</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,22 +12597,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>65127</t>
+          <t>72381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52886</t>
+          <t>59130</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79979</t>
+          <t>88115</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>111230</t>
+          <t>127670</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>76099</t>
+          <t>107999</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133665</t>
+          <t>148953</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24801</t>
+          <t>33205</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>23685</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36926</t>
+          <t>44871</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29917</t>
+          <t>38326</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>30055</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39762</t>
+          <t>49704</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>54717</t>
+          <t>71532</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36317</t>
+          <t>58364</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69535</t>
+          <t>89817</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>10656</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>20066</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15240</t>
+          <t>18722</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>11843</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25093</t>
+          <t>29684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>956983</t>
+          <t>1069600</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>956983</t>
+          <t>1069600</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>956983</t>
+          <t>1069600</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2149848</t>
+          <t>2118517</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2149848</t>
+          <t>2118517</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2149848</t>
+          <t>2118517</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>465264</t>
+          <t>513184</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>435045</t>
+          <t>481406</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>491162</t>
+          <t>542927</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,32 +13053,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>491406</t>
+          <t>539112</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>256051</t>
+          <t>514179</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>645633</t>
+          <t>565225</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>956670</t>
+          <t>1052296</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>571986</t>
+          <t>1006077</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1110116</t>
+          <t>1087820</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,45%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>185041</t>
+          <t>219861</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159804</t>
+          <t>191230</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>212205</t>
+          <t>249517</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>376899</t>
+          <t>194688</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207549</t>
+          <t>173927</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>650650</t>
+          <t>217485</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>561940</t>
+          <t>414548</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>394452</t>
+          <t>377689</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>995626</t>
+          <t>451422</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -13244,22 +13244,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27925</t>
+          <t>31154</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>21834</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39697</t>
+          <t>45537</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43293</t>
+          <t>50644</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19877</t>
+          <t>38648</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63241</t>
+          <t>67700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>71218</t>
+          <t>81798</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>44962</t>
+          <t>64248</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>91907</t>
+          <t>103644</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22785</t>
+          <t>33807</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>22909</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32559</t>
+          <t>50593</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16970</t>
+          <t>19700</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25962</t>
+          <t>28322</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>39755</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23756</t>
+          <t>39911</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51986</t>
+          <t>71506</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -13470,17 +13470,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>16931</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>20344</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>703230</t>
+          <t>800526</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>703230</t>
+          <t>800526</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>703230</t>
+          <t>800526</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1636596</t>
+          <t>1612785</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1636596</t>
+          <t>1612785</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1636596</t>
+          <t>1612785</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>581952</t>
+          <t>611413</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>553340</t>
+          <t>580429</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>611266</t>
+          <t>643043</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>711754</t>
+          <t>694314</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>671630</t>
+          <t>665528</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>783337</t>
+          <t>723316</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1293706</t>
+          <t>1305727</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1245327</t>
+          <t>1265899</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1374055</t>
+          <t>1353685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>64,28%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>233106</t>
+          <t>254576</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>207901</t>
+          <t>230980</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>260024</t>
+          <t>283843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>258981</t>
+          <t>282088</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>206299</t>
+          <t>256539</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>288934</t>
+          <t>311124</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>492087</t>
+          <t>536664</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>436058</t>
+          <t>498431</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>532656</t>
+          <t>572333</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>58994</t>
+          <t>65595</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46010</t>
+          <t>51630</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>74696</t>
+          <t>80931</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>62954</t>
+          <t>71146</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47858</t>
+          <t>57915</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>77964</t>
+          <t>86047</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>121947</t>
+          <t>136741</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>102306</t>
+          <t>115946</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>141198</t>
+          <t>159595</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>36398</t>
+          <t>41369</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26560</t>
+          <t>30409</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48020</t>
+          <t>55466</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>44143</t>
+          <t>50431</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32589</t>
+          <t>39550</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58227</t>
+          <t>64043</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>80541</t>
+          <t>91800</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>64728</t>
+          <t>74726</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>98325</t>
+          <t>108355</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>16381</t>
+          <t>17109</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>11128</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25941</t>
+          <t>26229</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>13939</t>
+          <t>17773</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9054</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20388</t>
+          <t>26293</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>30320</t>
+          <t>34882</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21843</t>
+          <t>25408</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40734</t>
+          <t>45585</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1091770</t>
+          <t>1115752</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1091770</t>
+          <t>1115752</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1091770</t>
+          <t>1115752</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2018601</t>
+          <t>2105815</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2018601</t>
+          <t>2105815</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2018601</t>
+          <t>2105815</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2281179</t>
+          <t>2187213</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2169161</t>
+          <t>2119264</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2556797</t>
+          <t>2248751</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2166021</t>
+          <t>2277399</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1754344</t>
+          <t>2224068</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2322690</t>
+          <t>2336773</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4447199</t>
+          <t>4464612</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4060136</t>
+          <t>4381026</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4717038</t>
+          <t>4544858</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>855856</t>
+          <t>964251</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>658539</t>
+          <t>909387</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>941043</t>
+          <t>1023148</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1120823</t>
+          <t>1025358</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>950691</t>
+          <t>979383</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1642442</t>
+          <t>1076054</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1976679</t>
+          <t>1989609</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1751425</t>
+          <t>1918534</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2456323</t>
+          <t>2070356</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>177097</t>
+          <t>201909</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>141997</t>
+          <t>175902</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>209352</t>
+          <t>227808</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>225555</t>
+          <t>252502</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>181287</t>
+          <t>225056</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>253925</t>
+          <t>279663</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>402652</t>
+          <t>454411</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>343444</t>
+          <t>416019</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>444644</t>
+          <t>492852</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>103924</t>
+          <t>131606</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>76777</t>
+          <t>108930</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>123938</t>
+          <t>157343</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>111223</t>
+          <t>131248</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>88489</t>
+          <t>114553</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>131191</t>
+          <t>152622</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>215146</t>
+          <t>262854</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>184483</t>
+          <t>236644</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>248875</t>
+          <t>294649</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>38168</t>
+          <t>43088</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>26896</t>
+          <t>32742</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>51303</t>
+          <t>56805</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>31795</t>
+          <t>41544</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>23161</t>
+          <t>31961</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41154</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>69963</t>
+          <t>84632</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>54987</t>
+          <t>68855</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>85450</t>
+          <t>104050</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3456223</t>
+          <t>3528067</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3456223</t>
+          <t>3528067</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3456223</t>
+          <t>3528067</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3655416</t>
+          <t>3728051</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3655416</t>
+          <t>3728051</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3655416</t>
+          <t>3728051</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7111639</t>
+          <t>7256118</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7111639</t>
+          <t>7256118</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7111639</t>
+          <t>7256118</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
